--- a/artfynd/A 37927-2022 artfynd.xlsx
+++ b/artfynd/A 37927-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37927-2022 artfynd.xlsx
+++ b/artfynd/A 37927-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104198278</v>
+        <v>104198200</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -720,21 +715,17 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kubbo, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624209.8305522661</v>
+        <v>624264</v>
       </c>
       <c r="R2" t="n">
-        <v>6716940.308437431</v>
+        <v>6716985</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,19 +755,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104198254</v>
+        <v>104198210</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -860,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624265.7912980245</v>
+        <v>624268</v>
       </c>
       <c r="R3" t="n">
-        <v>6716932.397369054</v>
+        <v>6716977</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,19 +869,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104198265</v>
+        <v>104198224</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,7 +929,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -989,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624229.1620393404</v>
+        <v>624266</v>
       </c>
       <c r="R4" t="n">
-        <v>6716922.770253425</v>
+        <v>6716957</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1022,19 +983,14 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera gamla blomstänglar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,15 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104198246</v>
+        <v>104198234</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1048,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1118,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624266.8274003936</v>
+        <v>624271</v>
       </c>
       <c r="R5" t="n">
-        <v>6716945.225451516</v>
+        <v>6716951</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1151,19 +1102,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,15 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104198210</v>
+        <v>104198246</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1162,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1247,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624268.6792794047</v>
+        <v>624267</v>
       </c>
       <c r="R6" t="n">
-        <v>6716977.270001238</v>
+        <v>6716945</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1280,19 +1216,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,15 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104198224</v>
+        <v>104198254</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1276,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1376,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624265.9284788257</v>
+        <v>624266</v>
       </c>
       <c r="R7" t="n">
-        <v>6716957.002742562</v>
+        <v>6716932</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1409,24 +1330,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera gamla blomstänglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1457,12 +1363,7 @@
         <v>104198260</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624255.0122169172</v>
+        <v>624255</v>
       </c>
       <c r="R8" t="n">
-        <v>6716916.281204103</v>
+        <v>6716916</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1543,19 +1444,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,15 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104198271</v>
+        <v>104198265</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1504,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1639,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624218.9955727208</v>
+        <v>624229</v>
       </c>
       <c r="R9" t="n">
-        <v>6716931.768092594</v>
+        <v>6716923</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1672,19 +1558,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1712,15 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104198234</v>
+        <v>104198271</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1618,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1768,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624270.5618714141</v>
+        <v>624219</v>
       </c>
       <c r="R10" t="n">
-        <v>6716951.258376183</v>
+        <v>6716932</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1801,19 +1672,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,15 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104198200</v>
+        <v>104198278</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1876,7 +1732,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1886,17 +1742,21 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kubbo, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624264.470362859</v>
+        <v>624210</v>
       </c>
       <c r="R11" t="n">
-        <v>6716984.996992846</v>
+        <v>6716941</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1926,19 +1786,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37927-2022 artfynd.xlsx
+++ b/artfynd/A 37927-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198200</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198210</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198224</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198234</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198246</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198254</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198260</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1585,6 +1625,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198265</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1699,6 +1744,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198271</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1813,8 +1863,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198278</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>